--- a/Apostas_Diarias/Apostas_20260412.xlsx
+++ b/Apostas_Diarias/Apostas_20260412.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="11_2B590F4F9556CB6779C1C8F050BB983158A7E44A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78D86C93-CB97-463C-AF06-49DA2574271E}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_2B590F4F95A6C422ED23D7F0507380F35999E4A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC8E8CED-03A6-4EEA-940D-D096CDEA4FE5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="41">
   <si>
     <t>Data</t>
   </si>
@@ -74,6 +74,18 @@
     <t>P1 ⭐</t>
   </si>
   <si>
+    <t>07:00:00</t>
+  </si>
+  <si>
+    <t>PORTUGAL 2</t>
+  </si>
+  <si>
+    <t>Feirense x Vizela</t>
+  </si>
+  <si>
+    <t>Lay_CS_0x1_B365</t>
+  </si>
+  <si>
     <t>07:15:00</t>
   </si>
   <si>
@@ -83,7 +95,22 @@
     <t>FC Dordrecht x ADO Den Haag</t>
   </si>
   <si>
-    <t>Lay_CS_0x1_B365</t>
+    <t>08:00:00</t>
+  </si>
+  <si>
+    <t>SCOTLAND 1</t>
+  </si>
+  <si>
+    <t>Falkirk x Rangers</t>
+  </si>
+  <si>
+    <t>08:30:00</t>
+  </si>
+  <si>
+    <t>CHINA 1</t>
+  </si>
+  <si>
+    <t>Shijiazhuang Gongfu FC x Foshan Nanshi FC</t>
   </si>
   <si>
     <t>10:00:00</t>
@@ -95,6 +122,12 @@
     <t>Crystal Palace x Newcastle</t>
   </si>
   <si>
+    <t>SWEDEN 2</t>
+  </si>
+  <si>
+    <t>IK Brage x Oddevold</t>
+  </si>
+  <si>
     <t>Nottm Forest x Aston Villa</t>
   </si>
   <si>
@@ -107,58 +140,22 @@
     <t>Sunderland x Tottenham</t>
   </si>
   <si>
-    <t>10:30:00</t>
-  </si>
-  <si>
-    <t>SLOVAKIA 1</t>
-  </si>
-  <si>
-    <t>KFC Komarno x FC Kosice</t>
-  </si>
-  <si>
-    <t>11:00:00</t>
+    <t>12:00:00</t>
+  </si>
+  <si>
+    <t>AUSTRIA 1</t>
+  </si>
+  <si>
+    <t>Austria Wien x Rapid Vienna</t>
+  </si>
+  <si>
+    <t>13:00:00</t>
   </si>
   <si>
     <t>DENMARK 1</t>
   </si>
   <si>
-    <t>Brondby x Midtjylland</t>
-  </si>
-  <si>
-    <t>11:30:00</t>
-  </si>
-  <si>
-    <t>GERMANY 3</t>
-  </si>
-  <si>
-    <t>Erzgebirge x Verl</t>
-  </si>
-  <si>
-    <t>12:00:00</t>
-  </si>
-  <si>
-    <t>AUSTRIA 1</t>
-  </si>
-  <si>
-    <t>Austria Wien x Rapid Vienna</t>
-  </si>
-  <si>
-    <t>13:00:00</t>
-  </si>
-  <si>
     <t>Randers x FC Copenhagen</t>
-  </si>
-  <si>
-    <t>13:30:00</t>
-  </si>
-  <si>
-    <t>SPAIN 2</t>
-  </si>
-  <si>
-    <t>Cadiz x Andorra CF</t>
-  </si>
-  <si>
-    <t>Mirandes x CD Castellon</t>
   </si>
 </sst>
 </file>
@@ -498,14 +495,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="31" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -548,6 +545,9 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1">
+        <v>500</v>
+      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -569,12 +569,14 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="H2">
-        <v>11.5</v>
+        <f>G2</f>
+        <v>9.6</v>
       </c>
       <c r="I2">
+        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
@@ -583,7 +585,7 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>44.523809523809526</v>
+        <v>54.360465116279073</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -612,17 +614,19 @@
         <v>11.5</v>
       </c>
       <c r="H3">
+        <f t="shared" ref="H3:H12" si="0">G3</f>
         <v>11.5</v>
       </c>
       <c r="I3">
+        <f t="shared" ref="I3:I12" si="1">$L$1</f>
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J13" si="0">IF(L3=1,"GREEN","RED")</f>
+        <f t="shared" ref="J3:J12" si="2">IF(L3=1,"GREEN","RED")</f>
         <v>GREEN</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K13" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <f t="shared" ref="K3:K12" si="3">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
         <v>44.523809523809526</v>
       </c>
       <c r="L3">
@@ -637,13 +641,13 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -652,17 +656,19 @@
         <v>11</v>
       </c>
       <c r="H4">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="I4">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>46.75</v>
       </c>
       <c r="L4">
@@ -677,36 +683,38 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="G5">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <f t="shared" si="0"/>
+        <v>10.5</v>
       </c>
       <c r="I5">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J5" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
+        <f t="shared" si="2"/>
+        <v>RED</v>
       </c>
       <c r="K5">
-        <f t="shared" si="1"/>
-        <v>54.360465116279073</v>
+        <f t="shared" si="3"/>
+        <v>-500</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -717,13 +725,13 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -732,17 +740,19 @@
         <v>11.5</v>
       </c>
       <c r="H6">
+        <f t="shared" si="0"/>
         <v>11.5</v>
       </c>
       <c r="I6">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>44.523809523809526</v>
       </c>
       <c r="L6">
@@ -757,33 +767,35 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
       </c>
       <c r="G7">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="H7">
-        <v>12.5</v>
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="I7">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J7" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K7">
-        <f t="shared" si="1"/>
-        <v>40.652173913043484</v>
+        <f t="shared" si="3"/>
+        <v>46.75</v>
       </c>
       <c r="L7">
         <v>1</v>
@@ -797,33 +809,35 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
         <v>27</v>
       </c>
-      <c r="D8" t="s">
-        <v>28</v>
-      </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
       <c r="G8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H8">
-        <v>12</v>
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="I8">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J8" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K8">
-        <f t="shared" si="1"/>
-        <v>42.5</v>
+        <f t="shared" si="3"/>
+        <v>46.75</v>
       </c>
       <c r="L8">
         <v>1</v>
@@ -837,33 +851,35 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
       </c>
       <c r="G9">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="H9">
-        <v>13</v>
+        <f t="shared" si="0"/>
+        <v>9.6</v>
       </c>
       <c r="I9">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K9">
-        <f t="shared" si="1"/>
-        <v>38.958333333333336</v>
+        <f t="shared" si="3"/>
+        <v>54.360465116279073</v>
       </c>
       <c r="L9">
         <v>1</v>
@@ -877,33 +893,35 @@
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" t="s">
         <v>34</v>
-      </c>
-      <c r="E10" t="s">
-        <v>35</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
       </c>
       <c r="G10">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="H10">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>11.5</v>
       </c>
       <c r="I10">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K10">
-        <f t="shared" si="1"/>
-        <v>51.944444444444443</v>
+        <f t="shared" si="3"/>
+        <v>44.523809523809526</v>
       </c>
       <c r="L10">
         <v>1</v>
@@ -917,10 +935,10 @@
         <v>12</v>
       </c>
       <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" t="s">
         <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>28</v>
       </c>
       <c r="E11" t="s">
         <v>37</v>
@@ -929,21 +947,23 @@
         <v>16</v>
       </c>
       <c r="G11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="H11">
-        <v>10.5</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="I11">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J11" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K11">
-        <f t="shared" si="1"/>
-        <v>49.210526315789473</v>
+        <f t="shared" si="3"/>
+        <v>51.944444444444443</v>
       </c>
       <c r="L11">
         <v>1</v>
@@ -969,63 +989,25 @@
         <v>16</v>
       </c>
       <c r="G12">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="H12">
-        <v>9.6</v>
+        <f t="shared" si="0"/>
+        <v>10.5</v>
       </c>
       <c r="I12">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J12" t="str">
-        <f t="shared" si="0"/>
-        <v>RED</v>
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
       </c>
       <c r="K12">
-        <f t="shared" si="1"/>
-        <v>-500</v>
+        <f t="shared" si="3"/>
+        <v>49.210526315789473</v>
       </c>
       <c r="L12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13">
-        <v>11.5</v>
-      </c>
-      <c r="H13">
-        <v>11.5</v>
-      </c>
-      <c r="I13">
-        <v>500</v>
-      </c>
-      <c r="J13" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K13">
-        <f t="shared" si="1"/>
-        <v>44.523809523809526</v>
-      </c>
-      <c r="L13">
         <v>1</v>
       </c>
     </row>

--- a/Apostas_Diarias/Apostas_20260412.xlsx
+++ b/Apostas_Diarias/Apostas_20260412.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_2B590F4F95A6C422ED23D7F0507380F35999E4A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC8E8CED-03A6-4EEA-940D-D096CDEA4FE5}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="11_2B590F4F9556CB6779C1C8F050BB983158A7E44A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78D86C93-CB97-463C-AF06-49DA2574271E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="42">
   <si>
     <t>Data</t>
   </si>
@@ -74,45 +74,18 @@
     <t>P1 ⭐</t>
   </si>
   <si>
-    <t>07:00:00</t>
-  </si>
-  <si>
-    <t>PORTUGAL 2</t>
-  </si>
-  <si>
-    <t>Feirense x Vizela</t>
+    <t>07:15:00</t>
+  </si>
+  <si>
+    <t>NETHERLANDS 2</t>
+  </si>
+  <si>
+    <t>FC Dordrecht x ADO Den Haag</t>
   </si>
   <si>
     <t>Lay_CS_0x1_B365</t>
   </si>
   <si>
-    <t>07:15:00</t>
-  </si>
-  <si>
-    <t>NETHERLANDS 2</t>
-  </si>
-  <si>
-    <t>FC Dordrecht x ADO Den Haag</t>
-  </si>
-  <si>
-    <t>08:00:00</t>
-  </si>
-  <si>
-    <t>SCOTLAND 1</t>
-  </si>
-  <si>
-    <t>Falkirk x Rangers</t>
-  </si>
-  <si>
-    <t>08:30:00</t>
-  </si>
-  <si>
-    <t>CHINA 1</t>
-  </si>
-  <si>
-    <t>Shijiazhuang Gongfu FC x Foshan Nanshi FC</t>
-  </si>
-  <si>
     <t>10:00:00</t>
   </si>
   <si>
@@ -122,12 +95,6 @@
     <t>Crystal Palace x Newcastle</t>
   </si>
   <si>
-    <t>SWEDEN 2</t>
-  </si>
-  <si>
-    <t>IK Brage x Oddevold</t>
-  </si>
-  <si>
     <t>Nottm Forest x Aston Villa</t>
   </si>
   <si>
@@ -140,6 +107,33 @@
     <t>Sunderland x Tottenham</t>
   </si>
   <si>
+    <t>10:30:00</t>
+  </si>
+  <si>
+    <t>SLOVAKIA 1</t>
+  </si>
+  <si>
+    <t>KFC Komarno x FC Kosice</t>
+  </si>
+  <si>
+    <t>11:00:00</t>
+  </si>
+  <si>
+    <t>DENMARK 1</t>
+  </si>
+  <si>
+    <t>Brondby x Midtjylland</t>
+  </si>
+  <si>
+    <t>11:30:00</t>
+  </si>
+  <si>
+    <t>GERMANY 3</t>
+  </si>
+  <si>
+    <t>Erzgebirge x Verl</t>
+  </si>
+  <si>
     <t>12:00:00</t>
   </si>
   <si>
@@ -152,10 +146,19 @@
     <t>13:00:00</t>
   </si>
   <si>
-    <t>DENMARK 1</t>
-  </si>
-  <si>
     <t>Randers x FC Copenhagen</t>
+  </si>
+  <si>
+    <t>13:30:00</t>
+  </si>
+  <si>
+    <t>SPAIN 2</t>
+  </si>
+  <si>
+    <t>Cadiz x Andorra CF</t>
+  </si>
+  <si>
+    <t>Mirandes x CD Castellon</t>
   </si>
 </sst>
 </file>
@@ -495,14 +498,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -545,9 +548,6 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1">
-        <v>500</v>
-      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -569,14 +569,12 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="H2">
-        <f>G2</f>
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="I2">
-        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
@@ -585,7 +583,7 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>54.360465116279073</v>
+        <v>44.523809523809526</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -614,19 +612,17 @@
         <v>11.5</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H12" si="0">G3</f>
         <v>11.5</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I12" si="1">$L$1</f>
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J12" si="2">IF(L3=1,"GREEN","RED")</f>
+        <f t="shared" ref="J3:J13" si="0">IF(L3=1,"GREEN","RED")</f>
         <v>GREEN</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K12" si="3">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <f t="shared" ref="K3:K13" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
         <v>44.523809523809526</v>
       </c>
       <c r="L3">
@@ -641,14 +637,14 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
         <v>20</v>
       </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
@@ -656,19 +652,17 @@
         <v>11</v>
       </c>
       <c r="H4">
+        <v>11</v>
+      </c>
+      <c r="I4">
+        <v>500</v>
+      </c>
+      <c r="J4" t="str">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="I4">
+        <v>GREEN</v>
+      </c>
+      <c r="K4">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J4" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="3"/>
         <v>46.75</v>
       </c>
       <c r="L4">
@@ -683,38 +677,36 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="G5">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="H5">
+        <v>9.6</v>
+      </c>
+      <c r="I5">
+        <v>500</v>
+      </c>
+      <c r="J5" t="str">
         <f t="shared" si="0"/>
-        <v>10.5</v>
-      </c>
-      <c r="I5">
+        <v>GREEN</v>
+      </c>
+      <c r="K5">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J5" t="str">
-        <f t="shared" si="2"/>
-        <v>RED</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="3"/>
-        <v>-500</v>
+        <v>54.360465116279073</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -725,13 +717,13 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -740,19 +732,17 @@
         <v>11.5</v>
       </c>
       <c r="H6">
+        <v>11.5</v>
+      </c>
+      <c r="I6">
+        <v>500</v>
+      </c>
+      <c r="J6" t="str">
         <f t="shared" si="0"/>
-        <v>11.5</v>
-      </c>
-      <c r="I6">
+        <v>GREEN</v>
+      </c>
+      <c r="K6">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J6" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="3"/>
         <v>44.523809523809526</v>
       </c>
       <c r="L6">
@@ -767,35 +757,33 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
         <v>26</v>
       </c>
-      <c r="D7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" t="s">
-        <v>30</v>
-      </c>
       <c r="F7" t="s">
         <v>16</v>
       </c>
       <c r="G7">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="H7">
+        <v>12.5</v>
+      </c>
+      <c r="I7">
+        <v>500</v>
+      </c>
+      <c r="J7" t="str">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="I7">
+        <v>GREEN</v>
+      </c>
+      <c r="K7">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J7" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="3"/>
-        <v>46.75</v>
+        <v>40.652173913043484</v>
       </c>
       <c r="L7">
         <v>1</v>
@@ -809,35 +797,33 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
       <c r="G8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H8">
+        <v>12</v>
+      </c>
+      <c r="I8">
+        <v>500</v>
+      </c>
+      <c r="J8" t="str">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="I8">
+        <v>GREEN</v>
+      </c>
+      <c r="K8">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J8" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="3"/>
-        <v>46.75</v>
+        <v>42.5</v>
       </c>
       <c r="L8">
         <v>1</v>
@@ -851,35 +837,33 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" t="s">
         <v>32</v>
       </c>
-      <c r="E9" t="s">
-        <v>33</v>
-      </c>
       <c r="F9" t="s">
         <v>16</v>
       </c>
       <c r="G9">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="H9">
+        <v>13</v>
+      </c>
+      <c r="I9">
+        <v>500</v>
+      </c>
+      <c r="J9" t="str">
         <f t="shared" si="0"/>
-        <v>9.6</v>
-      </c>
-      <c r="I9">
+        <v>GREEN</v>
+      </c>
+      <c r="K9">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J9" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="3"/>
-        <v>54.360465116279073</v>
+        <v>38.958333333333336</v>
       </c>
       <c r="L9">
         <v>1</v>
@@ -893,35 +877,33 @@
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
       </c>
       <c r="G10">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="H10">
+        <v>10</v>
+      </c>
+      <c r="I10">
+        <v>500</v>
+      </c>
+      <c r="J10" t="str">
         <f t="shared" si="0"/>
-        <v>11.5</v>
-      </c>
-      <c r="I10">
+        <v>GREEN</v>
+      </c>
+      <c r="K10">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J10" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="3"/>
-        <v>44.523809523809526</v>
+        <v>51.944444444444443</v>
       </c>
       <c r="L10">
         <v>1</v>
@@ -935,10 +917,10 @@
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E11" t="s">
         <v>37</v>
@@ -947,23 +929,21 @@
         <v>16</v>
       </c>
       <c r="G11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="H11">
+        <v>10.5</v>
+      </c>
+      <c r="I11">
+        <v>500</v>
+      </c>
+      <c r="J11" t="str">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="I11">
+        <v>GREEN</v>
+      </c>
+      <c r="K11">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J11" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="3"/>
-        <v>51.944444444444443</v>
+        <v>49.210526315789473</v>
       </c>
       <c r="L11">
         <v>1</v>
@@ -989,25 +969,63 @@
         <v>16</v>
       </c>
       <c r="G12">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="H12">
+        <v>9.6</v>
+      </c>
+      <c r="I12">
+        <v>500</v>
+      </c>
+      <c r="J12" t="str">
         <f t="shared" si="0"/>
-        <v>10.5</v>
-      </c>
-      <c r="I12">
+        <v>RED</v>
+      </c>
+      <c r="K12">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J12" t="str">
-        <f t="shared" si="2"/>
+        <v>-500</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13">
+        <v>11.5</v>
+      </c>
+      <c r="H13">
+        <v>11.5</v>
+      </c>
+      <c r="I13">
+        <v>500</v>
+      </c>
+      <c r="J13" t="str">
+        <f t="shared" si="0"/>
         <v>GREEN</v>
       </c>
-      <c r="K12">
-        <f t="shared" si="3"/>
-        <v>49.210526315789473</v>
-      </c>
-      <c r="L12">
+      <c r="K13">
+        <f t="shared" si="1"/>
+        <v>44.523809523809526</v>
+      </c>
+      <c r="L13">
         <v>1</v>
       </c>
     </row>
